--- a/results/exports/base-v1_BASE.xlsx
+++ b/results/exports/base-v1_BASE.xlsx
@@ -85,7 +85,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">09b582c51be772c4</t>
+          <t xml:space="preserve">961a30b0ed8e8317</t>
         </is>
       </c>
     </row>
@@ -97,7 +97,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">C:\Users\potap_fgzvmxm\OneDrive\Рабочий стол\хакатон\fuel-hub-2035\configs\assumptions.json</t>
+          <t xml:space="preserve">C:\Users\Андрей С\Desktop\19.09.26 Хакатон\hakaton-main\configs\assumptions.json</t>
         </is>
       </c>
     </row>
